--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/25.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/25.xlsx
@@ -426,13 +426,13 @@
         <v>-11.9025612621934</v>
       </c>
       <c r="E2">
-        <v>-6.697193985969347</v>
+        <v>-7.161163318899222</v>
       </c>
       <c r="F2">
-        <v>-4.392480428147096</v>
+        <v>-4.560007794954463</v>
       </c>
       <c r="G2">
-        <v>-4.913148680045309</v>
+        <v>-5.106312391170705</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.51994262252626</v>
       </c>
       <c r="E3">
-        <v>-6.948809587257536</v>
+        <v>-7.119791180365145</v>
       </c>
       <c r="F3">
-        <v>-4.94678081899558</v>
+        <v>-4.619564097746136</v>
       </c>
       <c r="G3">
-        <v>-5.264473704309386</v>
+        <v>-4.885062011690133</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.29401148924573</v>
       </c>
       <c r="E4">
-        <v>-7.665680608093776</v>
+        <v>-8.157681195131129</v>
       </c>
       <c r="F4">
-        <v>-4.991425680169459</v>
+        <v>-4.832919234378579</v>
       </c>
       <c r="G4">
-        <v>-5.464162500692685</v>
+        <v>-4.9771481464105</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.1258772422267</v>
       </c>
       <c r="E5">
-        <v>-8.187138918551025</v>
+        <v>-9.213648878135734</v>
       </c>
       <c r="F5">
-        <v>-4.523239051046401</v>
+        <v>-4.540556071601925</v>
       </c>
       <c r="G5">
-        <v>-5.081791180361323</v>
+        <v>-4.648712234004945</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.00807517599102</v>
       </c>
       <c r="E6">
-        <v>-7.673922430787736</v>
+        <v>-9.649632241698205</v>
       </c>
       <c r="F6">
-        <v>-4.363918320098569</v>
+        <v>-4.371552554082769</v>
       </c>
       <c r="G6">
-        <v>-5.600507318727568</v>
+        <v>-5.618327985365466</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.89712249421716</v>
       </c>
       <c r="E7">
-        <v>-9.755381166725323</v>
+        <v>-9.768636010145775</v>
       </c>
       <c r="F7">
-        <v>-4.587452435376613</v>
+        <v>-4.427707580318548</v>
       </c>
       <c r="G7">
-        <v>-5.205575788620212</v>
+        <v>-4.788576161948074</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.76109152587716</v>
       </c>
       <c r="E8">
-        <v>-10.8115707449563</v>
+        <v>-9.978770789523702</v>
       </c>
       <c r="F8">
-        <v>-4.454798507859703</v>
+        <v>-4.343342502180432</v>
       </c>
       <c r="G8">
-        <v>-6.016755451562292</v>
+        <v>-5.51869380681556</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.54930446198603</v>
       </c>
       <c r="E9">
-        <v>-9.811344048512114</v>
+        <v>-11.43598391197794</v>
       </c>
       <c r="F9">
-        <v>-4.600593655854625</v>
+        <v>-4.437018429926014</v>
       </c>
       <c r="G9">
-        <v>-4.499532430914307</v>
+        <v>-5.239724065857795</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.21652787648216</v>
       </c>
       <c r="E10">
-        <v>-10.89675134104058</v>
+        <v>-10.3858987167093</v>
       </c>
       <c r="F10">
-        <v>-4.62836218793127</v>
+        <v>-4.26440820073507</v>
       </c>
       <c r="G10">
-        <v>-5.321501161768872</v>
+        <v>-4.553378454110553</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.7084906749606</v>
       </c>
       <c r="E11">
-        <v>-12.14912347023186</v>
+        <v>-11.8176482298184</v>
       </c>
       <c r="F11">
-        <v>-4.216775418339293</v>
+        <v>-4.004775490777829</v>
       </c>
       <c r="G11">
-        <v>-4.680149174445864</v>
+        <v>-5.148472188613324</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.97969279355322</v>
       </c>
       <c r="E12">
-        <v>-11.61354537781869</v>
+        <v>-11.8160542069677</v>
       </c>
       <c r="F12">
-        <v>-4.245360720675098</v>
+        <v>-3.927772113748393</v>
       </c>
       <c r="G12">
-        <v>-4.321650197998188</v>
+        <v>-4.570537011640596</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.99073482207056</v>
       </c>
       <c r="E13">
-        <v>-12.27200361242999</v>
+        <v>-13.45619050848778</v>
       </c>
       <c r="F13">
-        <v>-4.342678151523387</v>
+        <v>-3.949891180137945</v>
       </c>
       <c r="G13">
-        <v>-4.884217822577619</v>
+        <v>-4.555189322520534</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.72277172662157</v>
       </c>
       <c r="E14">
-        <v>-12.46968508828683</v>
+        <v>-13.30239900271329</v>
       </c>
       <c r="F14">
-        <v>-3.186452871104671</v>
+        <v>-3.617122740554939</v>
       </c>
       <c r="G14">
-        <v>-4.620450106736187</v>
+        <v>-3.523345246658334</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.17588036484407</v>
       </c>
       <c r="E15">
-        <v>-12.80354230602832</v>
+        <v>-13.85815144683062</v>
       </c>
       <c r="F15">
-        <v>-3.493015079532712</v>
+        <v>-3.426454101982966</v>
       </c>
       <c r="G15">
-        <v>-4.825634408714676</v>
+        <v>-4.080864289290377</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.36706072235237</v>
       </c>
       <c r="E16">
-        <v>-14.20451178130729</v>
+        <v>-14.32821157730081</v>
       </c>
       <c r="F16">
-        <v>-3.641249769528878</v>
+        <v>-3.315736171659589</v>
       </c>
       <c r="G16">
-        <v>-3.037714700411565</v>
+        <v>-3.377747453841187</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.3288589253482</v>
       </c>
       <c r="E17">
-        <v>-14.75092651202081</v>
+        <v>-15.75344461631288</v>
       </c>
       <c r="F17">
-        <v>-2.868430199658899</v>
+        <v>-3.228286253313449</v>
       </c>
       <c r="G17">
-        <v>-2.111635933438</v>
+        <v>-3.091067452322459</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.10669952844316</v>
       </c>
       <c r="E18">
-        <v>-14.24861458966799</v>
+        <v>-16.48428597946279</v>
       </c>
       <c r="F18">
-        <v>-2.321779781775268</v>
+        <v>-2.798981533342994</v>
       </c>
       <c r="G18">
-        <v>-2.287674192488745</v>
+        <v>-2.637158553432986</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.76354412413908</v>
       </c>
       <c r="E19">
-        <v>-16.55689100322776</v>
+        <v>-16.73109686982884</v>
       </c>
       <c r="F19">
-        <v>-2.778080167035557</v>
+        <v>-2.609924897736868</v>
       </c>
       <c r="G19">
-        <v>-1.7591455971441</v>
+        <v>-2.596667270942161</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.37433185142981</v>
       </c>
       <c r="E20">
-        <v>-17.1186029191392</v>
+        <v>-17.28863353270519</v>
       </c>
       <c r="F20">
-        <v>-2.52649421802911</v>
+        <v>-2.178769604988559</v>
       </c>
       <c r="G20">
-        <v>-2.184037564381861</v>
+        <v>-3.086280403472673</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.01753719864405</v>
       </c>
       <c r="E21">
-        <v>-17.65616901164173</v>
+        <v>-17.75906046957001</v>
       </c>
       <c r="F21">
-        <v>-2.030425570495224</v>
+        <v>-1.996581791886447</v>
       </c>
       <c r="G21">
-        <v>-2.35824178120385</v>
+        <v>-2.458597658681317</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.766497838640227</v>
       </c>
       <c r="E22">
-        <v>-17.66200621463761</v>
+        <v>-17.70276700918065</v>
       </c>
       <c r="F22">
-        <v>-1.950807865942552</v>
+        <v>-1.590304857346415</v>
       </c>
       <c r="G22">
-        <v>-2.306527749334895</v>
+        <v>-2.835936949792986</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.681370961703376</v>
       </c>
       <c r="E23">
-        <v>-18.38733642492018</v>
+        <v>-18.17720164554225</v>
       </c>
       <c r="F23">
-        <v>-1.701465964230289</v>
+        <v>-1.568461637301995</v>
       </c>
       <c r="G23">
-        <v>-2.018361312869034</v>
+        <v>-2.419036639487026</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.806008693017489</v>
       </c>
       <c r="E24">
-        <v>-18.30501782440875</v>
+        <v>-19.35201460040416</v>
       </c>
       <c r="F24">
-        <v>-1.859308887731527</v>
+        <v>-1.26517065174761</v>
       </c>
       <c r="G24">
-        <v>-3.166094345878962</v>
+        <v>-1.863331775810504</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.170408772688202</v>
       </c>
       <c r="E25">
-        <v>-19.27055640995419</v>
+        <v>-18.55573678784342</v>
       </c>
       <c r="F25">
-        <v>-1.742200102895552</v>
+        <v>-1.193681716518609</v>
       </c>
       <c r="G25">
-        <v>-2.19512127084734</v>
+        <v>-2.645666655468914</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.788640629002534</v>
       </c>
       <c r="E26">
-        <v>-19.51503966468029</v>
+        <v>-19.77599750784631</v>
       </c>
       <c r="F26">
-        <v>-1.447404853424278</v>
+        <v>-1.205376607511333</v>
       </c>
       <c r="G26">
-        <v>-2.539967557491063</v>
+        <v>-2.62896826376883</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.65634440457651</v>
       </c>
       <c r="E27">
-        <v>-19.02390401617841</v>
+        <v>-19.96332689212161</v>
       </c>
       <c r="F27">
-        <v>-1.396355055491953</v>
+        <v>-1.099025001768113</v>
       </c>
       <c r="G27">
-        <v>-2.926079794281801</v>
+        <v>-2.759913582029162</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.753204968719687</v>
       </c>
       <c r="E28">
-        <v>-19.60087236102168</v>
+        <v>-20.22087932283385</v>
       </c>
       <c r="F28">
-        <v>-1.393166669358578</v>
+        <v>-1.402019431792296</v>
       </c>
       <c r="G28">
-        <v>-3.309464141548179</v>
+        <v>-3.028623942360726</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.044018940860521</v>
       </c>
       <c r="E29">
-        <v>-19.766958673727</v>
+        <v>-19.51117687635175</v>
       </c>
       <c r="F29">
-        <v>-1.395624435442684</v>
+        <v>-1.270574920683474</v>
       </c>
       <c r="G29">
-        <v>-2.484178244063265</v>
+        <v>-2.951594168752964</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.49008758041932</v>
       </c>
       <c r="E30">
-        <v>-20.91873980978589</v>
+        <v>-19.77995539412901</v>
       </c>
       <c r="F30">
-        <v>-1.466120158155727</v>
+        <v>-1.510936491381986</v>
       </c>
       <c r="G30">
-        <v>-2.892447962148345</v>
+        <v>-2.771745471786518</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.045551382951455</v>
       </c>
       <c r="E31">
-        <v>-19.24601208083261</v>
+        <v>-19.95329632219462</v>
       </c>
       <c r="F31">
-        <v>-1.398500527065204</v>
+        <v>-1.570419069474811</v>
       </c>
       <c r="G31">
-        <v>-3.445544115939922</v>
+        <v>-2.682744765508751</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.655466797193817</v>
       </c>
       <c r="E32">
-        <v>-19.48459020545272</v>
+        <v>-19.87831837804962</v>
       </c>
       <c r="F32">
-        <v>-1.92799959787387</v>
+        <v>-1.314200889951909</v>
       </c>
       <c r="G32">
-        <v>-3.150418912750513</v>
+        <v>-2.711771628797081</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.262558229514122</v>
       </c>
       <c r="E33">
-        <v>-19.14246399417322</v>
+        <v>-19.28533282064122</v>
       </c>
       <c r="F33">
-        <v>-1.796929508831113</v>
+        <v>-1.927008870460122</v>
       </c>
       <c r="G33">
-        <v>-2.275474832176531</v>
+        <v>-2.586689286686797</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.81939776285963</v>
       </c>
       <c r="E34">
-        <v>-19.06447008633912</v>
+        <v>-19.33770009406592</v>
       </c>
       <c r="F34">
-        <v>-2.108692207813929</v>
+        <v>-1.586964051610925</v>
       </c>
       <c r="G34">
-        <v>-1.937723044623467</v>
+        <v>-2.21097547343491</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.29798943943484</v>
       </c>
       <c r="E35">
-        <v>-18.88758789159951</v>
+        <v>-19.0397853745233</v>
       </c>
       <c r="F35">
-        <v>-2.279335892790627</v>
+        <v>-1.602847168192203</v>
       </c>
       <c r="G35">
-        <v>-2.407217991911828</v>
+        <v>-2.520501549720148</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.69022692298764</v>
       </c>
       <c r="E36">
-        <v>-17.6121703581832</v>
+        <v>-18.81491041225041</v>
       </c>
       <c r="F36">
-        <v>-2.041648292068351</v>
+        <v>-2.169945835413939</v>
       </c>
       <c r="G36">
-        <v>-1.339292280217111</v>
+        <v>-2.527384173896293</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.00376244611125</v>
       </c>
       <c r="E37">
-        <v>-18.32395137423482</v>
+        <v>-17.82289836765613</v>
       </c>
       <c r="F37">
-        <v>-2.093271320243414</v>
+        <v>-1.982265118063863</v>
       </c>
       <c r="G37">
-        <v>-2.943960050739405</v>
+        <v>-2.231000963401962</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.25021951239396</v>
       </c>
       <c r="E38">
-        <v>-18.63853540659967</v>
+        <v>-18.16550006870644</v>
       </c>
       <c r="F38">
-        <v>-2.139562147446656</v>
+        <v>-2.07915593969971</v>
       </c>
       <c r="G38">
-        <v>-1.822542544221143</v>
+        <v>-2.440171162209733</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.43656531555709</v>
       </c>
       <c r="E39">
-        <v>-16.92520537969362</v>
+        <v>-17.96177308004936</v>
       </c>
       <c r="F39">
-        <v>-1.748798877626253</v>
+        <v>-1.654543921066114</v>
       </c>
       <c r="G39">
-        <v>-1.941745357453681</v>
+        <v>-1.797878979953573</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.56266963527424</v>
       </c>
       <c r="E40">
-        <v>-17.82141755665562</v>
+        <v>-17.10795194827315</v>
       </c>
       <c r="F40">
-        <v>-1.441336233831369</v>
+        <v>-2.100871591164099</v>
       </c>
       <c r="G40">
-        <v>-1.499482957771365</v>
+        <v>-2.331466088882225</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.62436992045678</v>
       </c>
       <c r="E41">
-        <v>-18.00482981091429</v>
+        <v>-17.4106713787379</v>
       </c>
       <c r="F41">
-        <v>-2.142439895803981</v>
+        <v>-1.919639714044818</v>
       </c>
       <c r="G41">
-        <v>-0.688035140640604</v>
+        <v>-1.031120217057434</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.61587090629062</v>
       </c>
       <c r="E42">
-        <v>-17.46849093486784</v>
+        <v>-16.69365544673342</v>
       </c>
       <c r="F42">
-        <v>-1.864120045606986</v>
+        <v>-1.752925804027</v>
       </c>
       <c r="G42">
-        <v>-0.849993649512829</v>
+        <v>-1.432129908774892</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.52777918511404</v>
       </c>
       <c r="E43">
-        <v>-17.09201624824016</v>
+        <v>-16.24610183208135</v>
       </c>
       <c r="F43">
-        <v>-1.516650569726497</v>
+        <v>-1.771265858324981</v>
       </c>
       <c r="G43">
-        <v>-1.084535869333575</v>
+        <v>-1.608194652189952</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.35080168784278</v>
       </c>
       <c r="E44">
-        <v>-16.66155762296705</v>
+        <v>-16.14981288925625</v>
       </c>
       <c r="F44">
-        <v>-1.908957088018315</v>
+        <v>-1.957651837424481</v>
       </c>
       <c r="G44">
-        <v>-0.8962254179687511</v>
+        <v>-1.293424671770508</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.07644098498502</v>
       </c>
       <c r="E45">
-        <v>-16.93006443230385</v>
+        <v>-16.15853020172102</v>
       </c>
       <c r="F45">
-        <v>-1.986877467762651</v>
+        <v>-1.814338478168347</v>
       </c>
       <c r="G45">
-        <v>-2.103587997232032</v>
+        <v>-1.501687781100519</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.70533386203161</v>
       </c>
       <c r="E46">
-        <v>-15.44703900800589</v>
+        <v>-15.57281284509493</v>
       </c>
       <c r="F46">
-        <v>-2.32253773794883</v>
+        <v>-2.148015636792225</v>
       </c>
       <c r="G46">
-        <v>-1.232566913122086</v>
+        <v>-0.5788169327545083</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.2482134027906</v>
       </c>
       <c r="E47">
-        <v>-15.63993388683662</v>
+        <v>-14.78351341098</v>
       </c>
       <c r="F47">
-        <v>-2.214592353322624</v>
+        <v>-1.998957549597676</v>
       </c>
       <c r="G47">
-        <v>-1.49441782309628</v>
+        <v>-1.366634075825951</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.723747575296411</v>
       </c>
       <c r="E48">
-        <v>-15.29798881451743</v>
+        <v>-14.79890569413208</v>
       </c>
       <c r="F48">
-        <v>-2.428845440219702</v>
+        <v>-2.327184050711133</v>
       </c>
       <c r="G48">
-        <v>-1.138782468540072</v>
+        <v>-1.625697506456079</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.155971661818297</v>
       </c>
       <c r="E49">
-        <v>-14.93883554096909</v>
+        <v>-15.00906311588004</v>
       </c>
       <c r="F49">
-        <v>-2.451367921534418</v>
+        <v>-2.463014767217778</v>
       </c>
       <c r="G49">
-        <v>-1.231603544370158</v>
+        <v>-1.101648079226068</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.569190067581626</v>
       </c>
       <c r="E50">
-        <v>-13.79962544875549</v>
+        <v>-14.14233130470797</v>
       </c>
       <c r="F50">
-        <v>-2.433538141556561</v>
+        <v>-2.515136472569326</v>
       </c>
       <c r="G50">
-        <v>-1.384570611557723</v>
+        <v>-1.546678094979215</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.99155139681457</v>
       </c>
       <c r="E51">
-        <v>-12.93917463103205</v>
+        <v>-13.6995008884459</v>
       </c>
       <c r="F51">
-        <v>-2.280402830005433</v>
+        <v>-2.50147006715794</v>
       </c>
       <c r="G51">
-        <v>-1.848709096163543</v>
+        <v>-1.324457725655636</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.452729221714098</v>
       </c>
       <c r="E52">
-        <v>-14.41551149922068</v>
+        <v>-13.56012351543782</v>
       </c>
       <c r="F52">
-        <v>-2.690263281929975</v>
+        <v>-2.427951631792081</v>
       </c>
       <c r="G52">
-        <v>-1.851258216228782</v>
+        <v>-1.089250086181497</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.979713097688657</v>
       </c>
       <c r="E53">
-        <v>-13.63090809265172</v>
+        <v>-13.89581929362642</v>
       </c>
       <c r="F53">
-        <v>-2.400000030519418</v>
+        <v>-2.40614071807637</v>
       </c>
       <c r="G53">
-        <v>-1.631146664413719</v>
+        <v>-1.412826117735402</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.593679125625284</v>
       </c>
       <c r="E54">
-        <v>-12.45609966626382</v>
+        <v>-12.50119873890621</v>
       </c>
       <c r="F54">
-        <v>-2.610830303308128</v>
+        <v>-2.532395507406654</v>
       </c>
       <c r="G54">
-        <v>-1.625912691916131</v>
+        <v>-1.276749453889199</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.309561917594722</v>
       </c>
       <c r="E55">
-        <v>-14.41997657459224</v>
+        <v>-11.96178502900854</v>
       </c>
       <c r="F55">
-        <v>-2.32522744690572</v>
+        <v>-2.764050936701744</v>
       </c>
       <c r="G55">
-        <v>-1.561204768805537</v>
+        <v>-1.782716681383711</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.138855310134593</v>
       </c>
       <c r="E56">
-        <v>-12.89422952650592</v>
+        <v>-13.08654928913768</v>
       </c>
       <c r="F56">
-        <v>-2.521397273399685</v>
+        <v>-2.75366072436843</v>
       </c>
       <c r="G56">
-        <v>-1.293166449218445</v>
+        <v>-1.683562531937</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.090893987922914</v>
       </c>
       <c r="E57">
-        <v>-13.54784229392902</v>
+        <v>-12.83980179740773</v>
       </c>
       <c r="F57">
-        <v>-2.838150885984368</v>
+        <v>-2.960294487894558</v>
       </c>
       <c r="G57">
-        <v>-1.866999860268016</v>
+        <v>-1.326245420246843</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.171938732209788</v>
       </c>
       <c r="E58">
-        <v>-12.63708012998036</v>
+        <v>-12.34939070474707</v>
       </c>
       <c r="F58">
-        <v>-2.423088286770245</v>
+        <v>-2.85923117965081</v>
       </c>
       <c r="G58">
-        <v>-0.9602381265160989</v>
+        <v>-1.655456000308587</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.382155039107692</v>
       </c>
       <c r="E59">
-        <v>-11.29369473018293</v>
+        <v>-12.54853940618239</v>
       </c>
       <c r="F59">
-        <v>-2.598442068799261</v>
+        <v>-2.584834477473474</v>
       </c>
       <c r="G59">
-        <v>-2.598322543711796</v>
+        <v>-1.623846911499626</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.71678609941633</v>
       </c>
       <c r="E60">
-        <v>-13.15776859985631</v>
+        <v>-11.59919011521438</v>
       </c>
       <c r="F60">
-        <v>-2.559499688826254</v>
+        <v>-3.070270201025026</v>
       </c>
       <c r="G60">
-        <v>-0.9221205051769303</v>
+        <v>-1.831378390265458</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.163624669613315</v>
       </c>
       <c r="E61">
-        <v>-11.24037647721662</v>
+        <v>-11.32421211652062</v>
       </c>
       <c r="F61">
-        <v>-2.915165031790041</v>
+        <v>-3.153094515793935</v>
       </c>
       <c r="G61">
-        <v>-1.926824728708186</v>
+        <v>-1.60979364568542</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.70596912628773</v>
       </c>
       <c r="E62">
-        <v>-12.88375063765218</v>
+        <v>-11.54411028585908</v>
       </c>
       <c r="F62">
-        <v>-2.869866588735353</v>
+        <v>-3.014605568291705</v>
       </c>
       <c r="G62">
-        <v>-2.312294719664305</v>
+        <v>-1.837059286410847</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.327974560487885</v>
       </c>
       <c r="E63">
-        <v>-11.66708099753737</v>
+        <v>-10.5529812936963</v>
       </c>
       <c r="F63">
-        <v>-2.686553852700239</v>
+        <v>-3.091453212249415</v>
       </c>
       <c r="G63">
-        <v>-1.984792381100824</v>
+        <v>-1.648093347029248</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.011160145036801</v>
       </c>
       <c r="E64">
-        <v>-11.24710578959202</v>
+        <v>-10.8024186989868</v>
       </c>
       <c r="F64">
-        <v>-3.009571579584892</v>
+        <v>-2.971375558641807</v>
       </c>
       <c r="G64">
-        <v>-1.764468954371248</v>
+        <v>-2.297413817465281</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.738400921856481</v>
       </c>
       <c r="E65">
-        <v>-11.77341409571148</v>
+        <v>-10.56898944931342</v>
       </c>
       <c r="F65">
-        <v>-2.759254689439535</v>
+        <v>-3.027550465695253</v>
       </c>
       <c r="G65">
-        <v>-2.026376143619609</v>
+        <v>-2.749389357759819</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.48984937158228</v>
       </c>
       <c r="E66">
-        <v>-11.26182333011695</v>
+        <v>-10.24188418631737</v>
       </c>
       <c r="F66">
-        <v>-2.579604994059601</v>
+        <v>-2.660740267694201</v>
       </c>
       <c r="G66">
-        <v>-2.353828824000001</v>
+        <v>-2.462159805681572</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.24181753206052</v>
       </c>
       <c r="E67">
-        <v>-10.61091406167643</v>
+        <v>-10.88985900360091</v>
       </c>
       <c r="F67">
-        <v>-2.856068472906922</v>
+        <v>-2.961727563501401</v>
       </c>
       <c r="G67">
-        <v>-1.928095978195266</v>
+        <v>-2.435016642805088</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.97233367177698</v>
       </c>
       <c r="E68">
-        <v>-10.4800094635367</v>
+        <v>-10.00465554695155</v>
       </c>
       <c r="F68">
-        <v>-2.457038924773983</v>
+        <v>-3.067713859219987</v>
       </c>
       <c r="G68">
-        <v>-1.741291825050811</v>
+        <v>-2.735339402491152</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.66251545905979</v>
       </c>
       <c r="E69">
-        <v>-11.32009573364765</v>
+        <v>-9.856941253295346</v>
       </c>
       <c r="F69">
-        <v>-2.890617192175481</v>
+        <v>-3.211839846898267</v>
       </c>
       <c r="G69">
-        <v>-2.908249196007286</v>
+        <v>-2.28133780832658</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.29673587946088</v>
       </c>
       <c r="E70">
-        <v>-10.42087664994454</v>
+        <v>-10.15210266064129</v>
       </c>
       <c r="F70">
-        <v>-2.572164598047655</v>
+        <v>-3.016788316398082</v>
       </c>
       <c r="G70">
-        <v>-2.103541649594482</v>
+        <v>-2.307183237351671</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.86172898470935</v>
       </c>
       <c r="E71">
-        <v>-10.32122305093175</v>
+        <v>-11.3908531400175</v>
       </c>
       <c r="F71">
-        <v>-2.657506321353672</v>
+        <v>-3.47259168121669</v>
       </c>
       <c r="G71">
-        <v>-2.147691084906203</v>
+        <v>-2.396243533449144</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.34643595101011</v>
       </c>
       <c r="E72">
-        <v>-10.01133957458687</v>
+        <v>-10.02318606259093</v>
       </c>
       <c r="F72">
-        <v>-2.912348582620523</v>
+        <v>-3.318870713911783</v>
       </c>
       <c r="G72">
-        <v>-2.363416163881731</v>
+        <v>-2.456727200451629</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.74348500443026</v>
       </c>
       <c r="E73">
-        <v>-11.05453696088984</v>
+        <v>-10.42526474125798</v>
       </c>
       <c r="F73">
-        <v>-2.800358279966447</v>
+        <v>-3.306055041823072</v>
       </c>
       <c r="G73">
-        <v>-1.696546491542021</v>
+        <v>-1.713201846150095</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.05148733066798</v>
       </c>
       <c r="E74">
-        <v>-11.13909262756106</v>
+        <v>-10.39280011109699</v>
       </c>
       <c r="F74">
-        <v>-3.067772673305586</v>
+        <v>-3.37901101572243</v>
       </c>
       <c r="G74">
-        <v>-2.295096435587791</v>
+        <v>-2.002901065200638</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.27160166241624</v>
       </c>
       <c r="E75">
-        <v>-10.44950566262104</v>
+        <v>-11.01103643957216</v>
       </c>
       <c r="F75">
-        <v>-2.800622529167939</v>
+        <v>-3.550024152560777</v>
       </c>
       <c r="G75">
-        <v>-1.388513471294994</v>
+        <v>-1.664129629621478</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.40884821654794</v>
       </c>
       <c r="E76">
-        <v>-11.77975848779623</v>
+        <v>-11.52919802095183</v>
       </c>
       <c r="F76">
-        <v>-2.927474571395642</v>
+        <v>-3.297797047184563</v>
       </c>
       <c r="G76">
-        <v>-1.782865655932978</v>
+        <v>-1.54461231456271</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.4698458468011</v>
       </c>
       <c r="E77">
-        <v>-11.2888945477348</v>
+        <v>-11.85493115632355</v>
       </c>
       <c r="F77">
-        <v>-3.076830870855198</v>
+        <v>-3.518792216373027</v>
       </c>
       <c r="G77">
-        <v>-1.698704967233626</v>
+        <v>-1.625061881712539</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.46490654781679</v>
       </c>
       <c r="E78">
-        <v>-11.80179857079156</v>
+        <v>-11.56182114770308</v>
       </c>
       <c r="F78">
-        <v>-3.014667695846915</v>
+        <v>-3.378275425468744</v>
       </c>
       <c r="G78">
-        <v>-2.295172578135194</v>
+        <v>-1.584957933049807</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.41094450819844</v>
       </c>
       <c r="E79">
-        <v>-12.24564789370535</v>
+        <v>-12.38917787737847</v>
       </c>
       <c r="F79">
-        <v>-3.638672718538769</v>
+        <v>-3.627255330625983</v>
       </c>
       <c r="G79">
-        <v>-1.638287511141927</v>
+        <v>-1.257425799576473</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.32271933824084</v>
       </c>
       <c r="E80">
-        <v>-12.96344725171317</v>
+        <v>-12.98789648288058</v>
       </c>
       <c r="F80">
-        <v>-3.482009390219118</v>
+        <v>-3.663764795536968</v>
       </c>
       <c r="G80">
-        <v>-1.926920734528825</v>
+        <v>-1.503813151336731</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.21409538805199</v>
       </c>
       <c r="E81">
-        <v>-12.73513517766845</v>
+        <v>-13.63559959172366</v>
       </c>
       <c r="F81">
-        <v>-3.633015797545051</v>
+        <v>-3.71545574983906</v>
       </c>
       <c r="G81">
-        <v>-1.551471764920079</v>
+        <v>-1.256055233723215</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.09361552168048</v>
       </c>
       <c r="E82">
-        <v>-13.51694451577468</v>
+        <v>-13.569678595594</v>
       </c>
       <c r="F82">
-        <v>-3.547992995689112</v>
+        <v>-3.980274868105229</v>
       </c>
       <c r="G82">
-        <v>-2.315903214302111</v>
+        <v>-1.073250219590199</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-14.96965972808755</v>
       </c>
       <c r="E83">
-        <v>-14.51173704340967</v>
+        <v>-15.07429125548653</v>
       </c>
       <c r="F83">
-        <v>-3.743023817004228</v>
+        <v>-4.031794350354941</v>
       </c>
       <c r="G83">
-        <v>-1.280043446700774</v>
+        <v>-0.1805119567426346</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.84933308352543</v>
       </c>
       <c r="E84">
-        <v>-15.30592270097886</v>
+        <v>-15.13600982773707</v>
       </c>
       <c r="F84">
-        <v>-3.86172389562098</v>
+        <v>-3.81436530283553</v>
       </c>
       <c r="G84">
-        <v>-2.063798550395531</v>
+        <v>-0.9750197123489447</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.73541203784032</v>
       </c>
       <c r="E85">
-        <v>-17.31157931050206</v>
+        <v>-17.35065098424024</v>
       </c>
       <c r="F85">
-        <v>-3.839671098623652</v>
+        <v>-4.280524916923937</v>
       </c>
       <c r="G85">
-        <v>-1.771556832370828</v>
+        <v>-0.42491298117933</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.62437669905802</v>
       </c>
       <c r="E86">
-        <v>-17.32755123832711</v>
+        <v>-18.75483114759065</v>
       </c>
       <c r="F86">
-        <v>-3.74190303590824</v>
+        <v>-4.214532199412512</v>
       </c>
       <c r="G86">
-        <v>-1.809955850080834</v>
+        <v>-0.9054552189322392</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.50733169938063</v>
       </c>
       <c r="E87">
-        <v>-19.00098088075158</v>
+        <v>-19.28175532617515</v>
       </c>
       <c r="F87">
-        <v>-3.840858149111864</v>
+        <v>-4.460432234566142</v>
       </c>
       <c r="G87">
-        <v>-1.833576592503534</v>
+        <v>-0.6240720902763454</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.37678340761782</v>
       </c>
       <c r="E88">
-        <v>-19.6869631803815</v>
+        <v>-19.37555360829603</v>
       </c>
       <c r="F88">
-        <v>-3.878783293914233</v>
+        <v>-4.687133198425089</v>
       </c>
       <c r="G88">
-        <v>-1.315618569065782</v>
+        <v>-0.7902912712576124</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.23096308498139</v>
       </c>
       <c r="E89">
-        <v>-22.53874251586786</v>
+        <v>-21.91299344901396</v>
       </c>
       <c r="F89">
-        <v>-4.485921099550283</v>
+        <v>-4.428377729547413</v>
       </c>
       <c r="G89">
-        <v>-1.588417453138346</v>
+        <v>-0.6808247724560713</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-14.07527856924827</v>
       </c>
       <c r="E90">
-        <v>-23.12076010922969</v>
+        <v>-22.63859083926299</v>
       </c>
       <c r="F90">
-        <v>-4.381168242894466</v>
+        <v>-4.662768428006547</v>
       </c>
       <c r="G90">
-        <v>-1.16491260448154</v>
+        <v>-1.004831174930082</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.91828305747707</v>
       </c>
       <c r="E91">
-        <v>-24.35759957257465</v>
+        <v>-24.88923336412714</v>
       </c>
       <c r="F91">
-        <v>-4.2498885768988</v>
+        <v>-4.434606224049062</v>
       </c>
       <c r="G91">
-        <v>-1.981667226111752</v>
+        <v>-1.477567146301389</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.77382734176072</v>
       </c>
       <c r="E92">
-        <v>-26.20715515457944</v>
+        <v>-27.06147441849649</v>
       </c>
       <c r="F92">
-        <v>-4.866485509907418</v>
+        <v>-4.690958599091217</v>
       </c>
       <c r="G92">
-        <v>-2.373370974318319</v>
+        <v>-1.18585511556297</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.66024512235672</v>
       </c>
       <c r="E93">
-        <v>-27.67362900637936</v>
+        <v>-29.21376754486206</v>
       </c>
       <c r="F93">
-        <v>-4.83557663700676</v>
+        <v>-4.979896462657296</v>
       </c>
       <c r="G93">
-        <v>-2.048930890378664</v>
+        <v>-1.247689485145477</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-13.6002939243238</v>
       </c>
       <c r="E94">
-        <v>-29.94008043400429</v>
+        <v>-31.10520245448978</v>
       </c>
       <c r="F94">
-        <v>-4.896974400534857</v>
+        <v>-4.866588227465365</v>
       </c>
       <c r="G94">
-        <v>-2.884300709576198</v>
+        <v>-1.587156135287884</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-13.61916376816227</v>
       </c>
       <c r="E95">
-        <v>-32.30136716429786</v>
+        <v>-33.59885195155354</v>
       </c>
       <c r="F95">
-        <v>-4.718132363372652</v>
+        <v>-5.199418794603582</v>
       </c>
       <c r="G95">
-        <v>-3.527370870034087</v>
+        <v>-1.722458131477897</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-13.74074469188338</v>
       </c>
       <c r="E96">
-        <v>-35.43008079924929</v>
+        <v>-34.84674089147722</v>
       </c>
       <c r="F96">
-        <v>-4.856540130869408</v>
+        <v>-5.358333625524041</v>
       </c>
       <c r="G96">
-        <v>-2.689279782403272</v>
+        <v>-2.024608312301639</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-13.9682377865384</v>
       </c>
       <c r="E97">
-        <v>-36.97621050884413</v>
+        <v>-36.49830706139266</v>
       </c>
       <c r="F97">
-        <v>-4.931061719160057</v>
+        <v>-5.231218162462249</v>
       </c>
       <c r="G97">
-        <v>-2.727513272836315</v>
+        <v>-2.710142840391759</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-14.31546028939649</v>
       </c>
       <c r="E98">
-        <v>-39.15056183210106</v>
+        <v>-39.94664944875348</v>
       </c>
       <c r="F98">
-        <v>-4.880405395744061</v>
+        <v>-5.199681387070269</v>
       </c>
       <c r="G98">
-        <v>-3.585861588621931</v>
+        <v>-2.948800068317819</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-14.75330548178624</v>
       </c>
       <c r="E99">
-        <v>-42.44596406680083</v>
+        <v>-42.0348556109625</v>
       </c>
       <c r="F99">
-        <v>-5.52328725481091</v>
+        <v>-5.315236983025994</v>
       </c>
       <c r="G99">
-        <v>-3.732455855646398</v>
+        <v>-3.512453551834132</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-15.30337383129404</v>
       </c>
       <c r="E100">
-        <v>-44.78901689650252</v>
+        <v>-44.68449292369447</v>
       </c>
       <c r="F100">
-        <v>-5.32767243447682</v>
+        <v>-5.571290317435738</v>
       </c>
       <c r="G100">
-        <v>-3.614696440268983</v>
+        <v>-3.655780310411338</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-15.88738345881607</v>
       </c>
       <c r="E101">
-        <v>-46.50373716492892</v>
+        <v>-47.4518298043598</v>
       </c>
       <c r="F101">
-        <v>-4.858279702415286</v>
+        <v>-5.448932168368223</v>
       </c>
       <c r="G101">
-        <v>-4.292408149249805</v>
+        <v>-3.832364809476063</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.57636384430951</v>
       </c>
       <c r="E102">
-        <v>-49.41955931195026</v>
+        <v>-49.18587759985095</v>
       </c>
       <c r="F102">
-        <v>-5.393514389120936</v>
+        <v>-5.323657337675451</v>
       </c>
       <c r="G102">
-        <v>-4.340252153383353</v>
+        <v>-4.517750363016916</v>
       </c>
     </row>
   </sheetData>
